--- a/协作/32-依赖与许可证清单.xlsx
+++ b/协作/32-依赖与许可证清单.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>约束在 pyproject</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>通过（仅开发期）</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>通过（仅开发期）</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>通过（可选构建）</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>本机 bundled</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>通过（工具链）</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>本机 bundled</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -798,19 +798,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>通过（工具链）</t>
+          <t>通过</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"运行时,开发,构建,可选"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="I2:I121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,驳回"</formula1>
     </dataValidation>
   </dataValidations>
